--- a/Data/dim_date.xlsx
+++ b/Data/dim_date.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\2\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\2- Sysco\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37FCE3C-0AB0-4077-9C05-D6350CBCEB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB72587B-6466-49BE-B32F-34A97A24CE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
